--- a/output/pdf_financials_xlsx/SAG.xlsx
+++ b/output/pdf_financials_xlsx/SAG.xlsx
@@ -1231,13 +1231,13 @@
         <v>-3.095022</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.438621</v>
+        <v>-2.438621</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>21.449778</v>
+        <v>-21.449778</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
@@ -1495,13 +1495,13 @@
         <v>-3.095022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.438621</v>
+        <v>-2.438621</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>21.449778</v>
+        <v>-21.449778</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
         <v>-3.095022</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.438621</v>
+        <v>-2.438621</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>21.449778</v>
+        <v>-21.449778</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.37518</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-119.165433</v>
+        <v>119.165433</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -1902,13 +1902,13 @@
         <v>-3.095022</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.438621</v>
+        <v>-2.438621</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>21.449778</v>
+        <v>-21.449778</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2012,13 +2012,13 @@
         <v>-3.095022</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.453968</v>
+        <v>-2.423274</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>21.50579</v>
+        <v>-21.393766</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2144,13 +2144,13 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -5212,13 +5212,13 @@
         <v>13.765607</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>15.396357</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>15.980757</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>16.652457</v>
       </c>
     </row>
     <row r="93">
@@ -8726,7 +8726,11 @@
           <t>Share based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -45582,13 +45586,13 @@
         </is>
       </c>
       <c r="M449" s="5" t="n">
-        <v>1.500659</v>
+        <v>-1.500659</v>
       </c>
       <c r="N449" s="5" t="n">
-        <v>1.662966</v>
+        <v>-1.662966</v>
       </c>
       <c r="O449" s="5" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="P449" t="inlineStr">
         <is>
@@ -46014,13 +46018,13 @@
         </is>
       </c>
       <c r="M454" s="5" t="n">
-        <v>2.438621</v>
+        <v>-2.438621</v>
       </c>
       <c r="N454" s="5" t="n">
-        <v>21.449778</v>
+        <v>-21.449778</v>
       </c>
       <c r="O454" s="5" t="n">
-        <v>0.277585</v>
+        <v>-0.277585</v>
       </c>
       <c r="P454" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SAG.xlsx
+++ b/output/pdf_financials_xlsx/SAG.xlsx
@@ -999,13 +999,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004074</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00012</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         <v>-3.246741</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.154514</v>
+        <v>-2.158588</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.306446</v>
+        <v>-2.306568</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.420371</v>
+        <v>-1.420251</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.095022</v>
@@ -2000,13 +2000,13 @@
         <v>-3.235688</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.144703</v>
+        <v>-2.148777</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.29873</v>
+        <v>-2.298852</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.417906</v>
+        <v>-1.417786</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.095022</v>
@@ -2286,13 +2286,13 @@
         <v>1.794778</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.767145</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.433883</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.428636</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>3.260978</v>
@@ -2384,13 +2384,13 @@
         <v>1.809778</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.767145</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.433883</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.428636</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>3.260978</v>
@@ -2972,13 +2972,13 @@
         <v>0.038861</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.772888</v>
+        <v>0.005743</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.443974</v>
+        <v>0.010091</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.638588</v>
+        <v>0.209952</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.169842</v>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -45628,7 +45628,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -51986,7 +51986,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -53434,7 +53434,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -53520,7 +53520,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -55308,7 +55308,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -61894,7 +61894,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E640" s="5" t="n">

--- a/output/pdf_financials_xlsx/SAG.xlsx
+++ b/output/pdf_financials_xlsx/SAG.xlsx
@@ -736,7 +736,7 @@
         <v>0.430787</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.053964</v>
+        <v>0.417817</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.43144</v>
@@ -901,7 +901,7 @@
         <v>0.5248620000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.083662</v>
+        <v>0.447515</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.43144</v>
@@ -956,7 +956,7 @@
         <v>-0.5248620000000001</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.083662</v>
+        <v>-0.447515</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.43144</v>
@@ -1216,16 +1216,16 @@
         <v>-2.227597</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-3.246741</v>
+        <v>-3.238593</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-2.154514</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.306446</v>
+        <v>-2.167852</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.420371</v>
+        <v>-1.362741</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-3.095022</v>
@@ -1265,22 +1265,22 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.125</v>
+        <v>-0.125</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.008148000000000001</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.138594</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.05763</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1887,16 +1887,16 @@
         <v>-2.227597</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.246741</v>
+        <v>-3.238593</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.158588</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.306568</v>
+        <v>-2.167974</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.420251</v>
+        <v>-1.362621</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.095022</v>
@@ -1997,16 +1997,16 @@
         <v>-2.227597</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.235688</v>
+        <v>-3.22754</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.148777</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.298852</v>
+        <v>-2.160258</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.417786</v>
+        <v>-1.360156</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.095022</v>
@@ -2129,16 +2129,16 @@
         <v>-5.611427919861627</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2515907370886061</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.393148609775944</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.22897674613151</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -3914,40 +3914,40 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.063221</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.148332</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.241111</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.301508</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.066123</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.04325</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.032652</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.067896</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.057008</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.078302</v>
       </c>
     </row>
     <row r="68">
@@ -5485,7 +5485,7 @@
         <v>0.880186</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>4.739668</v>
+        <v>4.422979</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-2.102597</v>
@@ -5877,10 +5877,10 @@
         <v>0.185722</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.51914</v>
+        <v>0.6022110000000001</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.260854</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.019836</v>
@@ -6137,10 +6137,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.050164</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.022243</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -6281,10 +6281,10 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.200011</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.096428</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -31136,7 +31136,11 @@
           <t>Proceeds from disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -32840,7 +32844,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -33268,7 +33276,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -33354,7 +33366,11 @@
           <t>Units issued on private placement</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -34962,7 +34978,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -35976,7 +35996,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -38524,7 +38548,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -39386,7 +39414,11 @@
           <t>Deferred income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -40494,7 +40526,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -41258,7 +41294,11 @@
           <t>Expense recognized in respect of equity-settled share-based payments expense 9 (v)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -47872,7 +47912,11 @@
           <t>Management and director fees (Note 14)</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -53864,7 +53908,11 @@
           <t>Deferred income tax recovery (Note 18)</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -55394,7 +55442,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -56670,7 +56722,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
@@ -57772,7 +57828,11 @@
           <t>Deferred income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -59056,7 +59116,11 @@
           <t>Deferred income tax recovery (expense) 15</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
